--- a/config/sysopen.xlsx
+++ b/config/sysopen.xlsx
@@ -1445,7 +1445,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>実行中</t>
+          <t>运行中</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -1522,7 +1522,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>申請開始</t>
+          <t>申请开始</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>申請開始</t>
+          <t>申请开始</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="O9" s="6" t="inlineStr">
         <is>
-          <t>申請開始</t>
+          <t>申请开始</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="O10" s="6" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O12" s="6" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>クロスBOSS挑戦</t>
+          <t>跨BOSS挑战</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>釣り大会</t>
+          <t>钓鱼大赛</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="O14" s="6" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="O15" s="6" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>クロスアリーナ</t>
+          <t>十字竞技场</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O16" s="6" t="inlineStr">
         <is>
-          <t>絶賛開催中</t>
+          <t>好评举行中</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
